--- a/artfynd/A 47499-2023 artfynd.xlsx
+++ b/artfynd/A 47499-2023 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>136332257</v>
       </c>
       <c r="B7" t="n">
-        <v>101525</v>
+        <v>101528</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>136332247</v>
       </c>
       <c r="B8" t="n">
-        <v>97452</v>
+        <v>97455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47499-2023 artfynd.xlsx
+++ b/artfynd/A 47499-2023 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>136332257</v>
       </c>
       <c r="B7" t="n">
-        <v>101528</v>
+        <v>101529</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>136332247</v>
       </c>
       <c r="B8" t="n">
-        <v>97455</v>
+        <v>97456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47499-2023 artfynd.xlsx
+++ b/artfynd/A 47499-2023 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>136332257</v>
       </c>
       <c r="B7" t="n">
-        <v>101529</v>
+        <v>101534</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>136332247</v>
       </c>
       <c r="B8" t="n">
-        <v>97456</v>
+        <v>97461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47499-2023 artfynd.xlsx
+++ b/artfynd/A 47499-2023 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>136332257</v>
       </c>
       <c r="B7" t="n">
-        <v>101534</v>
+        <v>101536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>136332247</v>
       </c>
       <c r="B8" t="n">
-        <v>97461</v>
+        <v>97463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47499-2023 artfynd.xlsx
+++ b/artfynd/A 47499-2023 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>136332257</v>
       </c>
       <c r="B7" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>136332247</v>
       </c>
       <c r="B8" t="n">
-        <v>97463</v>
+        <v>97469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
